--- a/catalog/products.xlsx
+++ b/catalog/products.xlsx
@@ -394,7 +394,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W415"/>
+  <dimension ref="A1:W416"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" style="1" min="1" max="1"/>
@@ -21950,7 +21950,7 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>Hitachi</t>
+          <t>LG Sigma</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
@@ -21960,7 +21960,7 @@
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>Плата управления Hitachi LG GDC-1B</t>
+          <t>Плата управления LG Sigma LG GDC-1B</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
@@ -22074,7 +22074,7 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Hitachi</t>
+          <t>LG Sigma</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
@@ -22084,7 +22084,7 @@
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>Плата управления Hitachi LG HBDC</t>
+          <t>Плата управления LG Sigma LG HBDC</t>
         </is>
       </c>
       <c r="G311" t="inlineStr">
@@ -22441,7 +22441,7 @@
     <row r="317" ht="30" customHeight="1" s="1">
       <c r="A317" t="inlineStr">
         <is>
-          <t>SIO 20401704</t>
+          <t>SIO 204C1704</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
@@ -22456,7 +22456,7 @@
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>Плата управления Hyundai SIO 20401704</t>
+          <t>Плата управления Hyundai SIO 204C1704</t>
         </is>
       </c>
       <c r="G317" t="inlineStr">
@@ -28574,6 +28574,68 @@
       </c>
       <c r="W415" t="n">
         <v>21</v>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>Thyssen Mc2</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>ThyssenKrupp</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>Инструменты</t>
+        </is>
+      </c>
+      <c r="F416" t="inlineStr">
+        <is>
+          <t>Сервисный инструмент ThyssenKrupp Thyssen Mc2</t>
+        </is>
+      </c>
+      <c r="G416" t="inlineStr">
+        <is>
+          <t>Thyssen Mc2 Service Tool</t>
+        </is>
+      </c>
+      <c r="H416" t="inlineStr">
+        <is>
+          <t>Сервисный инструмент для лифтов ThyssenKrupp.</t>
+        </is>
+      </c>
+      <c r="L416" t="inlineStr">
+        <is>
+          <t>Thyssen-Mc2-tool.webp</t>
+        </is>
+      </c>
+      <c r="P416" t="inlineStr">
+        <is>
+          <t>По запросу</t>
+        </is>
+      </c>
+      <c r="R416" t="inlineStr">
+        <is>
+          <t>request</t>
+        </is>
+      </c>
+      <c r="S416" t="b">
+        <v>1</v>
+      </c>
+      <c r="T416" t="b">
+        <v>0</v>
+      </c>
+      <c r="U416" t="b">
+        <v>0</v>
+      </c>
+      <c r="V416" t="n">
+        <v>100</v>
+      </c>
+      <c r="W416" t="n">
+        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -31165,7 +31227,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C97"/>
+  <dimension ref="A1:C100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" style="1" min="1" max="1"/>
@@ -32822,6 +32884,57 @@
         </is>
       </c>
     </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Артикул</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>SIO 20401704</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>SIO 204C1704 — ошибка распознавания (C прочитана как 0)</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Марка</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Hitachi</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>LG Sigma — LG GDC-1B и LG HBDC (в PDF стоят на странице Hitachi)</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Позиция</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Thyssen Mc2 — сервисный инструмент возвращён отдельной строкой (был слит с платой)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
